--- a/examples/sales_analysis.xlsx
+++ b/examples/sales_analysis.xlsx
@@ -419,17 +419,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>revenue</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>margin</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -446,81 +446,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16344.45</t>
+          <t>January</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>12745.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7675.00</t>
+          <t>5975.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8669.45</t>
+          <t>6770.65</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12745.65</t>
+          <t>February</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>14345.08</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5975.00</t>
+          <t>6725.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6770.65</t>
+          <t>7620.08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14345.08</t>
+          <t>March</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>16344.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6725.00</t>
+          <t>7675.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7620.08</t>
+          <t>8669.45</t>
         </is>
       </c>
     </row>

--- a/examples/sales_analysis.xlsx
+++ b/examples/sales_analysis.xlsx
@@ -419,108 +419,108 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>margin</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>margin</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>profit</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>53.1%</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12745.65</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6770.65</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5975.00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>January</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>53.1%</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>12745.65</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5975.00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6770.65</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>53.1%</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14345.08</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7620.08</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6725.00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>February</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>53.1%</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>14345.08</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>6725.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>7620.08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>53.0%</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16344.45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8669.45</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7675.00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>March</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>53.0%</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>16344.45</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>7675.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>8669.45</t>
         </is>
       </c>
     </row>

--- a/examples/sales_analysis.xlsx
+++ b/examples/sales_analysis.xlsx
@@ -419,108 +419,108 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>margin</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>month</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>7675.00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12745.65</t>
+          <t>8669.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6770.65</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5975.00</t>
+          <t>16344.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>53.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>6725.00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7620.08</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14345.08</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>53.1%</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>14345.08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7620.08</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>6725.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>February</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>5975.00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16344.45</t>
+          <t>6770.65</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8669.45</t>
+          <t>January</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7675.00</t>
+          <t>12745.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
